--- a/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0003T0006Z000C1N9_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0003T0006Z000C1N9_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>41.40284580886638</v>
+        <v>6.727962443940787</v>
       </c>
       <c r="D2" t="n">
-        <v>38.31816158134698</v>
+        <v>6.226701256968886</v>
       </c>
       <c r="E2" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F2" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>46.98898045970922</v>
+        <v>7.635709324702749</v>
       </c>
       <c r="D3" t="n">
-        <v>31.83177031592038</v>
+        <v>5.172662676337062</v>
       </c>
       <c r="E3" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F3" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>78.94419234893702</v>
+        <v>12.82843125670227</v>
       </c>
       <c r="D4" t="n">
-        <v>30.59489733845319</v>
+        <v>4.971670817498643</v>
       </c>
       <c r="E4" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F4" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>35.9208055714088</v>
+        <v>5.83713090535393</v>
       </c>
       <c r="D5" t="n">
-        <v>33.82144973530993</v>
+        <v>5.495985581987863</v>
       </c>
       <c r="E5" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F5" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>62.09162028193978</v>
+        <v>10.08988829581521</v>
       </c>
       <c r="D6" t="n">
-        <v>18.85337886695536</v>
+        <v>3.063674065880247</v>
       </c>
       <c r="E6" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F6" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>88.20480005682934</v>
+        <v>14.33328000923477</v>
       </c>
       <c r="D7" t="n">
-        <v>44.32215811423035</v>
+        <v>7.202350693562433</v>
       </c>
       <c r="E7" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F7" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>61.02458235667677</v>
+        <v>9.916494632959976</v>
       </c>
       <c r="D8" t="n">
-        <v>15.57244121918691</v>
+        <v>2.530521698117873</v>
       </c>
       <c r="E8" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F8" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>73.34400919854158</v>
+        <v>11.91840149476301</v>
       </c>
       <c r="D9" t="n">
-        <v>24.98764295554968</v>
+        <v>4.060491980276823</v>
       </c>
       <c r="E9" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F9" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>42.49912214040636</v>
+        <v>6.906107347816033</v>
       </c>
       <c r="D10" t="n">
-        <v>22.14150352979529</v>
+        <v>3.597994323591734</v>
       </c>
       <c r="E10" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F10" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>65.96164239580176</v>
+        <v>10.71876688931779</v>
       </c>
       <c r="D11" t="n">
-        <v>16.28558644230625</v>
+        <v>2.646407796874767</v>
       </c>
       <c r="E11" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F11" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>30.71334236242905</v>
+        <v>4.990918133894721</v>
       </c>
       <c r="D12" t="n">
-        <v>27.33127633215993</v>
+        <v>4.441332403975989</v>
       </c>
       <c r="E12" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F12" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>55.21482750014872</v>
+        <v>8.972409468774167</v>
       </c>
       <c r="D13" t="n">
-        <v>17.59081247719804</v>
+        <v>2.858507027544682</v>
       </c>
       <c r="E13" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F13" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>75.91083202293966</v>
+        <v>12.3355102037277</v>
       </c>
       <c r="D14" t="n">
-        <v>34.07616369330589</v>
+        <v>5.537376600162208</v>
       </c>
       <c r="E14" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F14" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>59.35597131185518</v>
+        <v>9.645345338176467</v>
       </c>
       <c r="D15" t="n">
-        <v>9.79038626662614</v>
+        <v>1.590937768326748</v>
       </c>
       <c r="E15" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F15" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>49.74436486434058</v>
+        <v>8.083459290455345</v>
       </c>
       <c r="D16" t="n">
-        <v>7.591200071773972</v>
+        <v>1.233570011663271</v>
       </c>
       <c r="E16" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F16" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>27.73261652330986</v>
+        <v>4.506550185037852</v>
       </c>
       <c r="D17" t="n">
-        <v>23.88103099211808</v>
+        <v>3.880667536219188</v>
       </c>
       <c r="E17" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F17" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>56.26894933033332</v>
+        <v>9.143704266179165</v>
       </c>
       <c r="D18" t="n">
-        <v>14.10019578872851</v>
+        <v>2.291281815668382</v>
       </c>
       <c r="E18" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F18" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>15.82543936281551</v>
+        <v>2.571633896457521</v>
       </c>
       <c r="D19" t="n">
-        <v>12.61982160697286</v>
+        <v>2.050721011133089</v>
       </c>
       <c r="E19" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F19" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>40.73253787028219</v>
+        <v>6.619037403920856</v>
       </c>
       <c r="D20" t="n">
-        <v>11.09062610972416</v>
+        <v>1.802226742830177</v>
       </c>
       <c r="E20" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F20" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>38.23546588822693</v>
+        <v>6.213263206836876</v>
       </c>
       <c r="D21" t="n">
-        <v>8.702628901525365</v>
+        <v>1.414177196497872</v>
       </c>
       <c r="E21" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F21" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>67.80424892398931</v>
+        <v>11.01819045014826</v>
       </c>
       <c r="D22" t="n">
-        <v>34.41284628711375</v>
+        <v>5.592087521655984</v>
       </c>
       <c r="E22" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F22" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>12.70607541678577</v>
+        <v>2.064737255227687</v>
       </c>
       <c r="D23" t="n">
-        <v>9.620996457508271</v>
+        <v>1.563411924345094</v>
       </c>
       <c r="E23" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F23" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>34.90944879839753</v>
+        <v>5.6727854297396</v>
       </c>
       <c r="D24" t="n">
-        <v>6.824479019594762</v>
+        <v>1.108977840684149</v>
       </c>
       <c r="E24" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F24" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>57.53856280207079</v>
+        <v>9.350016455336503</v>
       </c>
       <c r="D25" t="n">
-        <v>21.87701236540272</v>
+        <v>3.555014509377943</v>
       </c>
       <c r="E25" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F25" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>5.726082616196301</v>
+        <v>0.9304884251318989</v>
       </c>
       <c r="D26" t="n">
-        <v>2.659450402947211</v>
+        <v>0.4321606904789217</v>
       </c>
       <c r="E26" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F26" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>40.84733254465092</v>
+        <v>6.637691538505774</v>
       </c>
       <c r="D27" t="n">
-        <v>10.67165584426935</v>
+        <v>1.734144074693769</v>
       </c>
       <c r="E27" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F27" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>57.81810731150829</v>
+        <v>9.395442438120098</v>
       </c>
       <c r="D28" t="n">
-        <v>30.17545254064824</v>
+        <v>4.90351103785534</v>
       </c>
       <c r="E28" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F28" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>28.60190636086242</v>
+        <v>4.647809783640143</v>
       </c>
       <c r="D29" t="n">
-        <v>5.487203815391134</v>
+        <v>0.8916706200010593</v>
       </c>
       <c r="E29" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F29" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>25.60549087822578</v>
+        <v>4.16089226771169</v>
       </c>
       <c r="D30" t="n">
-        <v>18.34002070943127</v>
+        <v>2.980253365282581</v>
       </c>
       <c r="E30" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F30" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>5.320556851299441</v>
+        <v>0.8645904883361591</v>
       </c>
       <c r="D31" t="n">
-        <v>8.395819596317798</v>
+        <v>1.364320684401642</v>
       </c>
       <c r="E31" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F31" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1440,16 +1440,16 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>8.035495625082095</v>
+        <v>1.305768039075841</v>
       </c>
       <c r="D32" t="n">
-        <v>8.954348169558591</v>
+        <v>1.455081577553271</v>
       </c>
       <c r="E32" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F32" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1472,16 +1472,16 @@
         <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>12.3963684647508</v>
+        <v>2.014409875522004</v>
       </c>
       <c r="D33" t="n">
-        <v>15.70950373770436</v>
+        <v>2.552794357376959</v>
       </c>
       <c r="E33" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F33" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1504,16 +1504,16 @@
         <v>33</v>
       </c>
       <c r="C34" t="n">
-        <v>30.68346269283719</v>
+        <v>4.986062687586044</v>
       </c>
       <c r="D34" t="n">
-        <v>4.297616190242835</v>
+        <v>0.6983626309144608</v>
       </c>
       <c r="E34" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F34" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1536,16 +1536,16 @@
         <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>38.02635261099203</v>
+        <v>6.179282299286206</v>
       </c>
       <c r="D35" t="n">
-        <v>12.35434177631356</v>
+        <v>2.007580538650954</v>
       </c>
       <c r="E35" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F35" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1568,16 +1568,16 @@
         <v>35</v>
       </c>
       <c r="C36" t="n">
-        <v>10.49586577299235</v>
+        <v>1.705578188111257</v>
       </c>
       <c r="D36" t="n">
-        <v>13.59276821586522</v>
+        <v>2.208824835078099</v>
       </c>
       <c r="E36" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F36" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1600,16 +1600,16 @@
         <v>36</v>
       </c>
       <c r="C37" t="n">
-        <v>49.13754871474617</v>
+        <v>7.984851666146253</v>
       </c>
       <c r="D37" t="n">
-        <v>23.93675056033865</v>
+        <v>3.88972196605503</v>
       </c>
       <c r="E37" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F37" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1632,16 +1632,16 @@
         <v>37</v>
       </c>
       <c r="C38" t="n">
-        <v>73.5165805690353</v>
+        <v>11.94644434246824</v>
       </c>
       <c r="D38" t="n">
-        <v>51.07923471104778</v>
+        <v>8.300375640545266</v>
       </c>
       <c r="E38" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F38" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1664,16 +1664,16 @@
         <v>38</v>
       </c>
       <c r="C39" t="n">
-        <v>18.7699793689416</v>
+        <v>3.05012164745301</v>
       </c>
       <c r="D39" t="n">
-        <v>7.060697366409636</v>
+        <v>1.147363322041566</v>
       </c>
       <c r="E39" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F39" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1696,16 +1696,16 @@
         <v>39</v>
       </c>
       <c r="C40" t="n">
-        <v>25.42938721902988</v>
+        <v>4.132275423092355</v>
       </c>
       <c r="D40" t="n">
-        <v>8.842704638414636</v>
+        <v>1.436939503742378</v>
       </c>
       <c r="E40" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F40" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1728,16 +1728,16 @@
         <v>40</v>
       </c>
       <c r="C41" t="n">
-        <v>38.50600426279123</v>
+        <v>6.257225692703575</v>
       </c>
       <c r="D41" t="n">
-        <v>17.49334596047818</v>
+        <v>2.842668718577704</v>
       </c>
       <c r="E41" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F41" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1760,16 +1760,16 @@
         <v>41</v>
       </c>
       <c r="C42" t="n">
-        <v>27.45359073947282</v>
+        <v>4.461208495164333</v>
       </c>
       <c r="D42" t="n">
-        <v>6.94472141669883</v>
+        <v>1.12851723021356</v>
       </c>
       <c r="E42" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F42" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1792,16 +1792,16 @@
         <v>42</v>
       </c>
       <c r="C43" t="n">
-        <v>7.750227810908207</v>
+        <v>1.259412019272584</v>
       </c>
       <c r="D43" t="n">
-        <v>5.096553038989175</v>
+        <v>0.8281898688357409</v>
       </c>
       <c r="E43" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F43" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>43</v>
       </c>
       <c r="C44" t="n">
-        <v>30.00691674368254</v>
+        <v>4.876123970848413</v>
       </c>
       <c r="D44" t="n">
-        <v>24.86550671183441</v>
+        <v>4.040644840673091</v>
       </c>
       <c r="E44" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F44" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1856,16 +1856,16 @@
         <v>44</v>
       </c>
       <c r="C45" t="n">
-        <v>24.95209114724885</v>
+        <v>4.054714811427938</v>
       </c>
       <c r="D45" t="n">
-        <v>10.98768418830099</v>
+        <v>1.78549868059891</v>
       </c>
       <c r="E45" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F45" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1888,16 +1888,16 @@
         <v>45</v>
       </c>
       <c r="C46" t="n">
-        <v>19.05263434968664</v>
+        <v>3.096053081824079</v>
       </c>
       <c r="D46" t="n">
-        <v>21.59408487542666</v>
+        <v>3.509038792256832</v>
       </c>
       <c r="E46" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F46" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -1920,16 +1920,16 @@
         <v>46</v>
       </c>
       <c r="C47" t="n">
-        <v>7.613818758230911</v>
+        <v>1.237245548212523</v>
       </c>
       <c r="D47" t="n">
-        <v>16.79960814822211</v>
+        <v>2.729936324086092</v>
       </c>
       <c r="E47" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F47" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -1952,16 +1952,16 @@
         <v>47</v>
       </c>
       <c r="C48" t="n">
-        <v>36.69558601841671</v>
+        <v>5.963032727992715</v>
       </c>
       <c r="D48" t="n">
-        <v>31.06138143493147</v>
+        <v>5.047474483176363</v>
       </c>
       <c r="E48" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F48" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -1984,16 +1984,16 @@
         <v>48</v>
       </c>
       <c r="C49" t="n">
-        <v>37.06367504948417</v>
+        <v>6.022847195541178</v>
       </c>
       <c r="D49" t="n">
-        <v>14.00466082793365</v>
+        <v>2.275757384539218</v>
       </c>
       <c r="E49" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F49" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2016,16 +2016,16 @@
         <v>49</v>
       </c>
       <c r="C50" t="n">
-        <v>34.19913573617657</v>
+        <v>5.557359557128692</v>
       </c>
       <c r="D50" t="n">
-        <v>35.92632297697034</v>
+        <v>5.83802748375768</v>
       </c>
       <c r="E50" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F50" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2048,16 +2048,16 @@
         <v>50</v>
       </c>
       <c r="C51" t="n">
-        <v>35.10596336808616</v>
+        <v>5.704719047314001</v>
       </c>
       <c r="D51" t="n">
-        <v>23.3223032281058</v>
+        <v>3.789874274567193</v>
       </c>
       <c r="E51" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F51" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2080,16 +2080,16 @@
         <v>51</v>
       </c>
       <c r="C52" t="n">
-        <v>19.55442195977101</v>
+        <v>3.17759356846279</v>
       </c>
       <c r="D52" t="n">
-        <v>10.33494771088597</v>
+        <v>1.67942900301897</v>
       </c>
       <c r="E52" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F52" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2112,16 +2112,16 @@
         <v>52</v>
       </c>
       <c r="C53" t="n">
-        <v>48.76674578309484</v>
+        <v>7.924596189752912</v>
       </c>
       <c r="D53" t="n">
-        <v>1.586114635575941</v>
+        <v>0.2577436282810904</v>
       </c>
       <c r="E53" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F53" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2144,16 +2144,16 @@
         <v>53</v>
       </c>
       <c r="C54" t="n">
-        <v>24.45688784636548</v>
+        <v>3.97424427503439</v>
       </c>
       <c r="D54" t="n">
-        <v>6.805760566651776</v>
+        <v>1.105936092080914</v>
       </c>
       <c r="E54" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F54" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2176,16 +2176,16 @@
         <v>54</v>
       </c>
       <c r="C55" t="n">
-        <v>27.4239130636313</v>
+        <v>4.456385872840086</v>
       </c>
       <c r="D55" t="n">
-        <v>22.13642290287554</v>
+        <v>3.597168721717276</v>
       </c>
       <c r="E55" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F55" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2208,16 +2208,16 @@
         <v>55</v>
       </c>
       <c r="C56" t="n">
-        <v>38.52789292517178</v>
+        <v>6.260782600340414</v>
       </c>
       <c r="D56" t="n">
-        <v>35.23390166475818</v>
+        <v>5.725509020523204</v>
       </c>
       <c r="E56" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F56" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2240,16 +2240,16 @@
         <v>56</v>
       </c>
       <c r="C57" t="n">
-        <v>38.76283170525282</v>
+        <v>6.298960152103584</v>
       </c>
       <c r="D57" t="n">
-        <v>17.88631613948702</v>
+        <v>2.906526372666641</v>
       </c>
       <c r="E57" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F57" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2272,16 +2272,16 @@
         <v>57</v>
       </c>
       <c r="C58" t="n">
-        <v>31.57749726306482</v>
+        <v>5.131343305248033</v>
       </c>
       <c r="D58" t="n">
-        <v>9.817029447310524</v>
+        <v>1.59526728518796</v>
       </c>
       <c r="E58" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F58" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2304,16 +2304,16 @@
         <v>58</v>
       </c>
       <c r="C59" t="n">
-        <v>70.00708553069592</v>
+        <v>11.37615139873809</v>
       </c>
       <c r="D59" t="n">
-        <v>64.99137025737291</v>
+        <v>10.5610976668231</v>
       </c>
       <c r="E59" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F59" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2336,16 +2336,16 @@
         <v>59</v>
       </c>
       <c r="C60" t="n">
-        <v>47.21149974315178</v>
+        <v>7.671868708262165</v>
       </c>
       <c r="D60" t="n">
-        <v>46.70499963731658</v>
+        <v>7.589562441063944</v>
       </c>
       <c r="E60" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F60" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2368,16 +2368,16 @@
         <v>60</v>
       </c>
       <c r="C61" t="n">
-        <v>44.65724257634655</v>
+        <v>7.256801918656314</v>
       </c>
       <c r="D61" t="n">
-        <v>22.53668165944344</v>
+        <v>3.662210769659559</v>
       </c>
       <c r="E61" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F61" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2400,16 +2400,16 @@
         <v>61</v>
       </c>
       <c r="C62" t="n">
-        <v>39.00940039391354</v>
+        <v>6.339027564010951</v>
       </c>
       <c r="D62" t="n">
-        <v>16.94650859839533</v>
+        <v>2.753807647239241</v>
       </c>
       <c r="E62" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F62" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -2432,16 +2432,16 @@
         <v>62</v>
       </c>
       <c r="C63" t="n">
-        <v>50.21258363283606</v>
+        <v>8.15954484033586</v>
       </c>
       <c r="D63" t="n">
-        <v>44.96098517232471</v>
+        <v>7.306160090502765</v>
       </c>
       <c r="E63" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F63" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2464,16 +2464,16 @@
         <v>63</v>
       </c>
       <c r="C64" t="n">
-        <v>43.17672188028812</v>
+        <v>7.01621730554682</v>
       </c>
       <c r="D64" t="n">
-        <v>32.07559995739738</v>
+        <v>5.212284993077074</v>
       </c>
       <c r="E64" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F64" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -2496,16 +2496,16 @@
         <v>64</v>
       </c>
       <c r="C65" t="n">
-        <v>67.7793221427256</v>
+        <v>11.01413984819291</v>
       </c>
       <c r="D65" t="n">
-        <v>22.2785193920928</v>
+        <v>3.62025940121508</v>
       </c>
       <c r="E65" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F65" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -2528,16 +2528,16 @@
         <v>65</v>
       </c>
       <c r="C66" t="n">
-        <v>45.14368258328025</v>
+        <v>7.335848419783042</v>
       </c>
       <c r="D66" t="n">
-        <v>22.54365897266429</v>
+        <v>3.663344583057947</v>
       </c>
       <c r="E66" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F66" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -2560,16 +2560,16 @@
         <v>66</v>
       </c>
       <c r="C67" t="n">
-        <v>81.99454696960277</v>
+        <v>13.32411388256045</v>
       </c>
       <c r="D67" t="n">
-        <v>78.52547465389446</v>
+        <v>12.76038963125785</v>
       </c>
       <c r="E67" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F67" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -2592,16 +2592,16 @@
         <v>67</v>
       </c>
       <c r="C68" t="n">
-        <v>42.34214281108024</v>
+        <v>6.880598206800538</v>
       </c>
       <c r="D68" t="n">
-        <v>26.88054368322236</v>
+        <v>4.368088348523633</v>
       </c>
       <c r="E68" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F68" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -2624,16 +2624,16 @@
         <v>68</v>
       </c>
       <c r="C69" t="n">
-        <v>74.77931194035553</v>
+        <v>12.15163819030777</v>
       </c>
       <c r="D69" t="n">
-        <v>28.98733791911889</v>
+        <v>4.71044241185682</v>
       </c>
       <c r="E69" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F69" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -2656,16 +2656,16 @@
         <v>69</v>
       </c>
       <c r="C70" t="n">
-        <v>48.65037751733725</v>
+        <v>7.905686346567304</v>
       </c>
       <c r="D70" t="n">
-        <v>27.30651623992625</v>
+        <v>4.437308888988015</v>
       </c>
       <c r="E70" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F70" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -2688,16 +2688,16 @@
         <v>70</v>
       </c>
       <c r="C71" t="n">
-        <v>73.12029097308896</v>
+        <v>11.88204728312696</v>
       </c>
       <c r="D71" t="n">
-        <v>30.7851306710984</v>
+        <v>5.00258373405349</v>
       </c>
       <c r="E71" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F71" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -2720,16 +2720,16 @@
         <v>71</v>
       </c>
       <c r="C72" t="n">
-        <v>49.77841685288171</v>
+        <v>8.088992738593278</v>
       </c>
       <c r="D72" t="n">
-        <v>31.57159289159826</v>
+        <v>5.130383844884718</v>
       </c>
       <c r="E72" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F72" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -2752,16 +2752,16 @@
         <v>72</v>
       </c>
       <c r="C73" t="n">
-        <v>77.68734307185946</v>
+        <v>12.62419324917716</v>
       </c>
       <c r="D73" t="n">
-        <v>33.84083828039753</v>
+        <v>5.499136220564599</v>
       </c>
       <c r="E73" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F73" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -2784,16 +2784,16 @@
         <v>73</v>
       </c>
       <c r="C74" t="n">
-        <v>88.45327677446106</v>
+        <v>14.37365747584992</v>
       </c>
       <c r="D74" t="n">
-        <v>85.72914425697124</v>
+        <v>13.93098594175783</v>
       </c>
       <c r="E74" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F74" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -2816,16 +2816,16 @@
         <v>74</v>
       </c>
       <c r="C75" t="n">
-        <v>83.63549293706147</v>
+        <v>13.59076760227249</v>
       </c>
       <c r="D75" t="n">
-        <v>39.25467894931849</v>
+        <v>6.378885329264254</v>
       </c>
       <c r="E75" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F75" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -2848,16 +2848,16 @@
         <v>75</v>
       </c>
       <c r="C76" t="n">
-        <v>61.95928143980111</v>
+        <v>10.06838323396768</v>
       </c>
       <c r="D76" t="n">
-        <v>23.22762390489022</v>
+        <v>3.774488884544661</v>
       </c>
       <c r="E76" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F76" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -2880,16 +2880,16 @@
         <v>76</v>
       </c>
       <c r="C77" t="n">
-        <v>60.78978886272603</v>
+        <v>9.878340690192982</v>
       </c>
       <c r="D77" t="n">
-        <v>39.96660215745172</v>
+        <v>6.494572850585905</v>
       </c>
       <c r="E77" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F77" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -2912,16 +2912,16 @@
         <v>77</v>
       </c>
       <c r="C78" t="n">
-        <v>75.80681705662069</v>
+        <v>12.31860777170086</v>
       </c>
       <c r="D78" t="n">
-        <v>66.7718498782219</v>
+        <v>10.85042560521106</v>
       </c>
       <c r="E78" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F78" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -2944,16 +2944,16 @@
         <v>78</v>
       </c>
       <c r="C79" t="n">
-        <v>79.55698609028227</v>
+        <v>12.92801023967087</v>
       </c>
       <c r="D79" t="n">
-        <v>45.35950625013719</v>
+        <v>7.370919765647295</v>
       </c>
       <c r="E79" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F79" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -2976,16 +2976,16 @@
         <v>79</v>
       </c>
       <c r="C80" t="n">
-        <v>63.95296152442656</v>
+        <v>10.39235624771931</v>
       </c>
       <c r="D80" t="n">
-        <v>45.49167444253587</v>
+        <v>7.39239709691208</v>
       </c>
       <c r="E80" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F80" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -3008,16 +3008,16 @@
         <v>80</v>
       </c>
       <c r="C81" t="n">
-        <v>88.9587831132109</v>
+        <v>14.45580225589677</v>
       </c>
       <c r="D81" t="n">
-        <v>83.06964613318063</v>
+        <v>13.49881749664185</v>
       </c>
       <c r="E81" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F81" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -3040,16 +3040,16 @@
         <v>81</v>
       </c>
       <c r="C82" t="n">
-        <v>70.69353886316991</v>
+        <v>11.48770006526511</v>
       </c>
       <c r="D82" t="n">
-        <v>56.13877073726065</v>
+        <v>9.122550244804856</v>
       </c>
       <c r="E82" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F82" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -3072,16 +3072,16 @@
         <v>82</v>
       </c>
       <c r="C83" t="n">
-        <v>90.29666498741878</v>
+        <v>14.67320806045555</v>
       </c>
       <c r="D83" t="n">
-        <v>48.57242062478947</v>
+        <v>7.893018351528289</v>
       </c>
       <c r="E83" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F83" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -3104,16 +3104,16 @@
         <v>83</v>
       </c>
       <c r="C84" t="n">
-        <v>71.83597514084056</v>
+        <v>11.67334596038659</v>
       </c>
       <c r="D84" t="n">
-        <v>49.22514606667976</v>
+        <v>7.999086235835461</v>
       </c>
       <c r="E84" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F84" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -3136,16 +3136,16 @@
         <v>84</v>
       </c>
       <c r="C85" t="n">
-        <v>100.6212054101336</v>
+        <v>16.35094587914671</v>
       </c>
       <c r="D85" t="n">
-        <v>55.98757394945631</v>
+        <v>9.097980766786652</v>
       </c>
       <c r="E85" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F85" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -3168,16 +3168,16 @@
         <v>85</v>
       </c>
       <c r="C86" t="n">
-        <v>84.07700177534369</v>
+        <v>13.66251278849335</v>
       </c>
       <c r="D86" t="n">
-        <v>56.82734647382574</v>
+        <v>9.234443801996683</v>
       </c>
       <c r="E86" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F86" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -3200,16 +3200,16 @@
         <v>86</v>
       </c>
       <c r="C87" t="n">
-        <v>80.18179534029231</v>
+        <v>13.0295417427975</v>
       </c>
       <c r="D87" t="n">
-        <v>57.56044716636806</v>
+        <v>9.353572664534809</v>
       </c>
       <c r="E87" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F87" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -3232,16 +3232,16 @@
         <v>87</v>
       </c>
       <c r="C88" t="n">
-        <v>71.60484138650483</v>
+        <v>11.63578672530704</v>
       </c>
       <c r="D88" t="n">
-        <v>51.39320752823253</v>
+        <v>8.351396223337787</v>
       </c>
       <c r="E88" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F88" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -3264,16 +3264,16 @@
         <v>88</v>
       </c>
       <c r="C89" t="n">
-        <v>82.32285327339692</v>
+        <v>13.377463656927</v>
       </c>
       <c r="D89" t="n">
-        <v>69.6107503215423</v>
+        <v>11.31174692725062</v>
       </c>
       <c r="E89" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F89" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -3296,16 +3296,16 @@
         <v>89</v>
       </c>
       <c r="C90" t="n">
-        <v>93.88902538491845</v>
+        <v>15.25696662504925</v>
       </c>
       <c r="D90" t="n">
-        <v>85.37722805945666</v>
+        <v>13.87379955966171</v>
       </c>
       <c r="E90" t="n">
-        <v>24.08846363264187</v>
+        <v>3.914375340304304</v>
       </c>
       <c r="F90" t="n">
-        <v>20.01444487731087</v>
+        <v>3.252347292563016</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
